--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364962</v>
       </c>
       <c r="B6" t="n">
-        <v>92836</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520554</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,12 +1206,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B7" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364962</v>
+        <v>129364945</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,43 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520554</v>
+        <v>520368</v>
       </c>
       <c r="R8" t="n">
-        <v>6831510</v>
+        <v>6831687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,18 +1426,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R10" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364964</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520641</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92836</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364962</v>
+        <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>92822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,43 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520554</v>
+        <v>520492</v>
       </c>
       <c r="R6" t="n">
-        <v>6831510</v>
+        <v>6831703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,18 +1197,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1235,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R7" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364945</v>
+        <v>129364962</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1338,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520368</v>
+        <v>520554</v>
       </c>
       <c r="R8" t="n">
-        <v>6831687</v>
+        <v>6831510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,12 +1420,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R22" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R23" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B6" t="n">
         <v>92822</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B7" t="n">
         <v>92822</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1449,54 +1449,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R9" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1533,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,7 +1543,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1571,45 +1561,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R10" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R22" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R23" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R6" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R7" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
         <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1561,51 +1561,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1654,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1655,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,42 +1673,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R22" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R23" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,45 +1449,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B9" t="n">
-        <v>79662</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R9" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1553,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1564,7 +1574,7 @@
         <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,54 +1683,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78709</v>
+        <v>78802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129364951</v>
       </c>
       <c r="B22" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129364944</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,54 +1449,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R9" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1533,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,7 +1543,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1683,45 +1673,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,45 +1449,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R9" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1553,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,54 +1683,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R22" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R23" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1449,51 +1449,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R9" t="n">
         <v>6831427</v>
@@ -1542,7 +1533,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,7 +1543,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R10" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,45 +1673,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364963</v>
+        <v>129364952</v>
       </c>
       <c r="B16" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520631</v>
+        <v>520456</v>
       </c>
       <c r="R16" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364949</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520324</v>
       </c>
       <c r="R17" t="n">
         <v>6831937</v>
@@ -2462,32 +2462,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364949</v>
+        <v>129364963</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>80053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520324</v>
+        <v>520631</v>
       </c>
       <c r="R18" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1449,42 +1449,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R9" t="n">
         <v>6831427</v>
@@ -1533,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1553,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1561,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364956</v>
+        <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520445</v>
+        <v>520641</v>
       </c>
       <c r="R10" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,54 +1683,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,51 +1449,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R9" t="n">
         <v>6831427</v>
@@ -1542,7 +1533,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,7 +1543,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1571,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R10" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,45 +1673,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>80053</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R15" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364952</v>
+        <v>129364949</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520456</v>
+        <v>520324</v>
       </c>
       <c r="R16" t="n">
         <v>6831937</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364949</v>
+        <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520324</v>
+        <v>520456</v>
       </c>
       <c r="R17" t="n">
         <v>6831937</v>
@@ -2462,32 +2462,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B18" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R18" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364962</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520554</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,12 +1206,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B7" t="n">
         <v>92835</v>
@@ -1255,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364962</v>
+        <v>129364945</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,43 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520554</v>
+        <v>520368</v>
       </c>
       <c r="R8" t="n">
-        <v>6831510</v>
+        <v>6831687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,18 +1426,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R9" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,45 +1561,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R10" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,7 +1665,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,51 +1683,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R15" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364949</v>
+        <v>129364952</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,21 +2249,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520324</v>
+        <v>520456</v>
       </c>
       <c r="R16" t="n">
         <v>6831937</v>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364963</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>80053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520631</v>
       </c>
       <c r="R17" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364958</v>
+        <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520493</v>
+        <v>520324</v>
       </c>
       <c r="R18" t="n">
-        <v>6831703</v>
+        <v>6831937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364962</v>
+        <v>129364945</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,43 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520554</v>
+        <v>520368</v>
       </c>
       <c r="R6" t="n">
-        <v>6831510</v>
+        <v>6831687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,18 +1197,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364945</v>
+        <v>129364962</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1338,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520368</v>
+        <v>520554</v>
       </c>
       <c r="R8" t="n">
-        <v>6831687</v>
+        <v>6831510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,12 +1420,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364952</v>
+        <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>80053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520456</v>
+        <v>520631</v>
       </c>
       <c r="R16" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364963</v>
+        <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520631</v>
+        <v>520456</v>
       </c>
       <c r="R17" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R22" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R23" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B6" t="n">
         <v>92835</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R6" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B7" t="n">
         <v>92835</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R7" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364951</v>
+        <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520451</v>
+        <v>520366</v>
       </c>
       <c r="R22" t="n">
-        <v>6831951</v>
+        <v>6831684</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364944</v>
+        <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520366</v>
+        <v>520451</v>
       </c>
       <c r="R23" t="n">
-        <v>6831684</v>
+        <v>6831951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1561,51 +1561,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1654,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1655,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,42 +1673,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364958</v>
+        <v>129364949</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520493</v>
+        <v>520324</v>
       </c>
       <c r="R15" t="n">
-        <v>6831703</v>
+        <v>6831937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B16" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R16" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364963</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>80053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520631</v>
       </c>
       <c r="R17" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364949</v>
+        <v>129364952</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520324</v>
+        <v>520456</v>
       </c>
       <c r="R18" t="n">
         <v>6831937</v>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1449,45 +1449,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B9" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R9" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1553,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1673,54 +1683,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364949</v>
+        <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520324</v>
+        <v>520493</v>
       </c>
       <c r="R15" t="n">
-        <v>6831937</v>
+        <v>6831703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>80053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R16" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364963</v>
+        <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>80053</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520631</v>
+        <v>520456</v>
       </c>
       <c r="R17" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364952</v>
+        <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520456</v>
+        <v>520324</v>
       </c>
       <c r="R18" t="n">
         <v>6831937</v>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1449,51 +1449,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>78828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R9" t="n">
         <v>6831427</v>
@@ -1542,7 +1533,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,7 +1543,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1571,42 +1561,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1655,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1686,7 +1686,7 @@
         <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364945</v>
+        <v>129364962</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520368</v>
+        <v>520554</v>
       </c>
       <c r="R6" t="n">
-        <v>6831687</v>
+        <v>6831510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,12 +1206,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1220,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B7" t="n">
         <v>92863</v>
@@ -1255,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R7" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364962</v>
+        <v>129364957</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,43 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520554</v>
+        <v>520492</v>
       </c>
       <c r="R8" t="n">
-        <v>6831510</v>
+        <v>6831703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,18 +1426,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1561,54 +1561,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364966</v>
+        <v>129364956</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520634</v>
+        <v>520445</v>
       </c>
       <c r="R10" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1655,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,45 +1673,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B15" t="n">
-        <v>79689</v>
+        <v>80079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R15" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364963</v>
+        <v>129364949</v>
       </c>
       <c r="B16" t="n">
-        <v>80079</v>
+        <v>78827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520631</v>
+        <v>520324</v>
       </c>
       <c r="R16" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364958</v>
       </c>
       <c r="B17" t="n">
         <v>79689</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520493</v>
       </c>
       <c r="R17" t="n">
-        <v>6831937</v>
+        <v>6831703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364949</v>
+        <v>129364952</v>
       </c>
       <c r="B18" t="n">
-        <v>78827</v>
+        <v>79689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520324</v>
+        <v>520456</v>
       </c>
       <c r="R18" t="n">
         <v>6831937</v>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364962</v>
+        <v>129364957</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,43 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520554</v>
+        <v>520492</v>
       </c>
       <c r="R6" t="n">
-        <v>6831510</v>
+        <v>6831703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,18 +1197,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1238,7 +1223,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364957</v>
+        <v>129364962</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1338,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520492</v>
+        <v>520554</v>
       </c>
       <c r="R8" t="n">
-        <v>6831703</v>
+        <v>6831510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,12 +1420,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>78828</v>
+        <v>79694</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R9" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,45 +1561,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B10" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R10" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,7 +1665,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,51 +1683,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78736</v>
+        <v>78833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78828</v>
+        <v>78741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>80079</v>
+        <v>79694</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R15" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2241,7 +2241,7 @@
         <v>129364949</v>
       </c>
       <c r="B16" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B17" t="n">
-        <v>79689</v>
+        <v>80084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R17" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2465,7 +2465,7 @@
         <v>129364952</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364962</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1124,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520554</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,12 +1206,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1223,7 +1238,7 @@
         <v>129364945</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364962</v>
+        <v>129364957</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,43 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520554</v>
+        <v>520492</v>
       </c>
       <c r="R8" t="n">
-        <v>6831510</v>
+        <v>6831703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,18 +1426,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
         <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129364964</v>
       </c>
       <c r="B11" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78833</v>
+        <v>78742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78741</v>
+        <v>78834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364949</v>
+        <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>78832</v>
+        <v>80085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520324</v>
+        <v>520631</v>
       </c>
       <c r="R16" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364963</v>
+        <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>80084</v>
+        <v>79695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520631</v>
+        <v>520456</v>
       </c>
       <c r="R17" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364952</v>
+        <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520456</v>
+        <v>520324</v>
       </c>
       <c r="R18" t="n">
         <v>6831937</v>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364956</v>
+        <v>129364964</v>
       </c>
       <c r="B9" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520445</v>
+        <v>520641</v>
       </c>
       <c r="R9" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B11" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78742</v>
+        <v>78834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78834</v>
+        <v>78742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129364960</v>
       </c>
       <c r="B2" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129364948</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129364943</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129364965</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B7" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B8" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R8" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364964</v>
+        <v>129364956</v>
       </c>
       <c r="B9" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520641</v>
+        <v>520445</v>
       </c>
       <c r="R9" t="n">
-        <v>6831427</v>
+        <v>6831776</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,51 +1561,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1654,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1655,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,45 +1673,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364956</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>79695</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520445</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
-        <v>6831776</v>
+        <v>6831427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
         <v>129364946</v>
       </c>
       <c r="B12" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>129364954</v>
       </c>
       <c r="B13" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>129364953</v>
       </c>
       <c r="B14" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364963</v>
+        <v>129364952</v>
       </c>
       <c r="B16" t="n">
-        <v>80085</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520631</v>
+        <v>520456</v>
       </c>
       <c r="R16" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364949</v>
       </c>
       <c r="B17" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520324</v>
       </c>
       <c r="R17" t="n">
         <v>6831937</v>
@@ -2462,32 +2462,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364949</v>
+        <v>129364963</v>
       </c>
       <c r="B18" t="n">
-        <v>78833</v>
+        <v>80090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520324</v>
+        <v>520631</v>
       </c>
       <c r="R18" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         <v>129364950</v>
       </c>
       <c r="B20" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129364947</v>
       </c>
       <c r="B21" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>129364944</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>129364951</v>
       </c>
       <c r="B23" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1561,42 +1561,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B10" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1645,6 +1654,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,7 +1665,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1673,51 +1683,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1766,7 +1767,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364946</v>
+        <v>129364954</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>78747</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520312</v>
+        <v>520480</v>
       </c>
       <c r="R12" t="n">
-        <v>6831789</v>
+        <v>6831864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364954</v>
+        <v>129364946</v>
       </c>
       <c r="B13" t="n">
-        <v>78747</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520480</v>
+        <v>520312</v>
       </c>
       <c r="R13" t="n">
-        <v>6831864</v>
+        <v>6831789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>80090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R15" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364952</v>
+        <v>129364958</v>
       </c>
       <c r="B16" t="n">
         <v>79700</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520456</v>
+        <v>520493</v>
       </c>
       <c r="R16" t="n">
-        <v>6831937</v>
+        <v>6831703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364949</v>
+        <v>129364952</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520324</v>
+        <v>520456</v>
       </c>
       <c r="R17" t="n">
         <v>6831937</v>
@@ -2462,32 +2462,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364963</v>
+        <v>129364949</v>
       </c>
       <c r="B18" t="n">
-        <v>80090</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520631</v>
+        <v>520324</v>
       </c>
       <c r="R18" t="n">
-        <v>6831479</v>
+        <v>6831937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364962</v>
+        <v>129364945</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>92875</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,43 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520554</v>
+        <v>520368</v>
       </c>
       <c r="R6" t="n">
-        <v>6831510</v>
+        <v>6831687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,18 +1197,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1342,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364945</v>
+        <v>129364962</v>
       </c>
       <c r="B8" t="n">
-        <v>92875</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1338,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520368</v>
+        <v>520554</v>
       </c>
       <c r="R8" t="n">
-        <v>6831687</v>
+        <v>6831510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,12 +1420,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B15" t="n">
-        <v>80090</v>
+        <v>79700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R15" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>80090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R16" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364945</v>
+        <v>129364957</v>
       </c>
       <c r="B6" t="n">
         <v>92875</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520368</v>
+        <v>520492</v>
       </c>
       <c r="R6" t="n">
-        <v>6831687</v>
+        <v>6831703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364957</v>
+        <v>129364945</v>
       </c>
       <c r="B7" t="n">
         <v>92875</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520492</v>
+        <v>520368</v>
       </c>
       <c r="R7" t="n">
-        <v>6831703</v>
+        <v>6831687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1561,51 +1561,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364966</v>
+        <v>129364964</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520634</v>
+        <v>520641</v>
       </c>
       <c r="R10" t="n">
         <v>6831427</v>
@@ -1654,7 +1645,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1665,7 +1655,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1683,42 +1673,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364964</v>
+        <v>129364966</v>
       </c>
       <c r="B11" t="n">
-        <v>78839</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520641</v>
+        <v>520634</v>
       </c>
       <c r="R11" t="n">
         <v>6831427</v>
@@ -1767,6 +1766,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2126,32 +2126,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364958</v>
+        <v>129364963</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>80090</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520493</v>
+        <v>520631</v>
       </c>
       <c r="R15" t="n">
-        <v>6831703</v>
+        <v>6831479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>silverlåga</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2238,32 +2238,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129364963</v>
+        <v>129364958</v>
       </c>
       <c r="B16" t="n">
-        <v>80090</v>
+        <v>79700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520631</v>
+        <v>520493</v>
       </c>
       <c r="R16" t="n">
-        <v>6831479</v>
+        <v>6831703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>silverlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129364960</v>
+        <v>129364954</v>
       </c>
       <c r="B2" t="n">
-        <v>78839</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520552</v>
+        <v>520480</v>
       </c>
       <c r="R2" t="n">
-        <v>6831581</v>
+        <v>6831864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>klen silverved</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129364948</v>
+        <v>129364943</v>
       </c>
       <c r="B3" t="n">
-        <v>92875</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520258</v>
+        <v>520484</v>
       </c>
       <c r="R3" t="n">
-        <v>6831870</v>
+        <v>6831861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,14 +894,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129364943</v>
+        <v>129364945</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520484</v>
+        <v>520368</v>
       </c>
       <c r="R4" t="n">
-        <v>6831861</v>
+        <v>6831687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129364965</v>
+        <v>129364948</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520641</v>
+        <v>520258</v>
       </c>
       <c r="R5" t="n">
-        <v>6831427</v>
+        <v>6831870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,11 +1091,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1113,14 +1108,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129364957</v>
+        <v>129364950</v>
       </c>
       <c r="B6" t="n">
-        <v>92875</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520492</v>
+        <v>520326</v>
       </c>
       <c r="R6" t="n">
-        <v>6831703</v>
+        <v>6831941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,14 +1215,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129364945</v>
+        <v>129364953</v>
       </c>
       <c r="B7" t="n">
-        <v>92875</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520368</v>
+        <v>520493</v>
       </c>
       <c r="R7" t="n">
-        <v>6831687</v>
+        <v>6831911</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,54 +1322,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129364962</v>
+        <v>129364957</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520554</v>
+        <v>520492</v>
       </c>
       <c r="R8" t="n">
-        <v>6831510</v>
+        <v>6831703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,18 +1406,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tallåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1449,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129364956</v>
+        <v>129364944</v>
       </c>
       <c r="B9" t="n">
-        <v>79700</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520445</v>
+        <v>520366</v>
       </c>
       <c r="R9" t="n">
-        <v>6831776</v>
+        <v>6831684</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,7 +1523,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1561,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129364964</v>
+        <v>129364947</v>
       </c>
       <c r="B10" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520641</v>
+        <v>520269</v>
       </c>
       <c r="R10" t="n">
-        <v>6831427</v>
+        <v>6831863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,54 +1653,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129364966</v>
+        <v>129364949</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520634</v>
+        <v>520324</v>
       </c>
       <c r="R11" t="n">
-        <v>6831427</v>
+        <v>6831937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1737,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,7 +1747,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129364954</v>
+        <v>129364951</v>
       </c>
       <c r="B12" t="n">
-        <v>78747</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520480</v>
+        <v>520451</v>
       </c>
       <c r="R12" t="n">
-        <v>6831864</v>
+        <v>6831951</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1859,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>klen silverved</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1907,10 +1877,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129364946</v>
+        <v>129364965</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520312</v>
+        <v>520641</v>
       </c>
       <c r="R13" t="n">
-        <v>6831789</v>
+        <v>6831427</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,32 +1989,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129364953</v>
+        <v>129364952</v>
       </c>
       <c r="B14" t="n">
-        <v>92875</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520493</v>
+        <v>520456</v>
       </c>
       <c r="R14" t="n">
-        <v>6831911</v>
+        <v>6831937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,6 +2079,11 @@
       <c r="AI14" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2126,32 +2101,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129364963</v>
+        <v>129364956</v>
       </c>
       <c r="B15" t="n">
-        <v>80090</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2136,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520631</v>
+        <v>520445</v>
       </c>
       <c r="R15" t="n">
-        <v>6831479</v>
+        <v>6831776</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,7 +2195,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2241,7 +2216,7 @@
         <v>129364958</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,32 +2325,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129364952</v>
+        <v>129364963</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520456</v>
+        <v>520631</v>
       </c>
       <c r="R17" t="n">
-        <v>6831937</v>
+        <v>6831479</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2444,7 +2419,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,45 +2437,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129364949</v>
+        <v>129364955</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520324</v>
+        <v>520479</v>
       </c>
       <c r="R18" t="n">
-        <v>6831937</v>
+        <v>6831866</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,6 +2530,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2556,7 +2541,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2574,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129364955</v>
+        <v>129364962</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520479</v>
+        <v>520554</v>
       </c>
       <c r="R19" t="n">
-        <v>6831866</v>
+        <v>6831510</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129364950</v>
+        <v>129364966</v>
       </c>
       <c r="B20" t="n">
-        <v>92875</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,34 +2692,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyran SO, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520326</v>
+        <v>520634</v>
       </c>
       <c r="R20" t="n">
-        <v>6831941</v>
+        <v>6831427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2780,12 +2774,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
           <t>brandpräglad tallskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129364947</v>
+        <v>129364946</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,21 +2814,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520269</v>
+        <v>520312</v>
       </c>
       <c r="R21" t="n">
-        <v>6831863</v>
+        <v>6831789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129364944</v>
+        <v>129364960</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,21 +2926,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520366</v>
+        <v>520552</v>
       </c>
       <c r="R22" t="n">
-        <v>6831684</v>
+        <v>6831581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129364951</v>
+        <v>129364964</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520451</v>
+        <v>520641</v>
       </c>
       <c r="R23" t="n">
-        <v>6831951</v>
+        <v>6831427</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 29934-2024 artfynd.xlsx
+++ b/artfynd/A 29934-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364943</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364948</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364950</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364953</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364957</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364944</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364947</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364949</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364951</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364965</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364952</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364956</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2322,6 +2397,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2434,6 +2514,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2556,6 +2641,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364955</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2678,6 +2768,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364962</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2800,6 +2895,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364966</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364946</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364960</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,8 +3246,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129364964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>